--- a/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-ex-bildgebung-modalitaet-mg-cr-dx.xlsx
+++ b/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-ex-bildgebung-modalitaet-mg-cr-dx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T06:44:38+00:00</t>
+    <t>2026-09-08T13:41:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-ex-bildgebung-modalitaet-mg-cr-dx.xlsx
+++ b/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-ex-bildgebung-modalitaet-mg-cr-dx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T13:41:14+00:00</t>
+    <t>2026-09-10T11:56:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-ex-bildgebung-modalitaet-mg-cr-dx.xlsx
+++ b/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-ex-bildgebung-modalitaet-mg-cr-dx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:56:08+00:00</t>
+    <t>2026-09-10T13:12:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-ex-bildgebung-modalitaet-mg-cr-dx.xlsx
+++ b/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-ex-bildgebung-modalitaet-mg-cr-dx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:12:52+00:00</t>
+    <t>2026-09-11T13:12:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-ex-bildgebung-modalitaet-mg-cr-dx.xlsx
+++ b/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-ex-bildgebung-modalitaet-mg-cr-dx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T13:12:48+00:00</t>
+    <t>2026-09-14T06:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-ex-bildgebung-modalitaet-mg-cr-dx.xlsx
+++ b/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-ex-bildgebung-modalitaet-mg-cr-dx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T06:55:37+00:00</t>
+    <t>2026-09-14T07:07:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-ex-bildgebung-modalitaet-mg-cr-dx.xlsx
+++ b/branches/migration/2026.0.0-template-v0.11.3/StructureDefinition-mii-ex-bildgebung-modalitaet-mg-cr-dx.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:07:04+00:00</t>
+    <t>2026-09-14T07:37:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
